--- a/tools/keybind_sheet/MidnightHelper_Keybinds.xlsx
+++ b/tools/keybind_sheet/MidnightHelper_Keybinds.xlsx
@@ -109,11 +109,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="008F5FC6"/>
+      <color rgb="004A7EC0"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="004A7EC0"/>
+      <color rgb="008F5FC6"/>
     </font>
     <font>
       <b val="1"/>
@@ -852,7 +852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -999,32 +999,32 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Nature's Cure</t>
+          <t>Barkskin</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>Dispel / CC</t>
+          <t>Defensive</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Barkskin</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
+          <t>Ironbark</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -1033,15 +1033,15 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Mass Entanglement</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
+          <t>Typhoon</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -1050,46 +1050,46 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Typhoon</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Tranquility</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Big cooldown</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Tranquility</t>
+          <t>Convoke the Spirits</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>Big cooldown</t>
+          <t>Cooldown</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Convoke the Spirits</t>
+          <t>Incarnation: Tree of Life</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
@@ -1101,80 +1101,80 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Incarnation: Tree of Life</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>Cooldown</t>
+          <t>Recuperate</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>Sustain / HoT</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>Shift+Q</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Recuperate</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>Sustain / HoT</t>
+          <t>Dash</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Movement</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Shift+Q</t>
+          <t>Shift+4</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Dash</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>Movement</t>
+          <t>Wild Growth</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>Raid heal</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Shift+4</t>
+          <t>Shift+F</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Wild Growth</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>Raid heal</t>
+          <t>Innervate</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Shift+F</t>
+          <t>Shift+R</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Innervate</t>
+          <t>Cat Form</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
@@ -1186,12 +1186,12 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Shift+R</t>
+          <t>Shift+X</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Cat Form</t>
+          <t>Moonkin Form</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
@@ -1203,158 +1203,141 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Shift+X</t>
+          <t>Shift+C</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Moonkin Form</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
+          <t>Mass Entanglement</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Shift+Z</t>
+          <t>Shift+V</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Ironbark</t>
+          <t>Nature's Cure</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Shift+C</t>
+          <t>Ctrl+F</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Entangling Roots</t>
-        </is>
-      </c>
-      <c r="C23" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Prowl</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Shift+V</t>
+          <t>Ctrl+R</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Cyclone</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Mark of the Wild</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+F</t>
+          <t>Ctrl+X</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Prowl</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
+          <t>Entangling Roots</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+R</t>
+          <t>Ctrl+C</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Mark of the Wild</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
+          <t>Soothe</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+X</t>
+          <t>Ctrl+V</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Ursol's Vortex</t>
-        </is>
-      </c>
-      <c r="C27" s="13" t="inlineStr">
+          <t>Cyclone</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Ctrl+V</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Soothe</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="18" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
         <is>
           <t>Situational (no fixed key — bind where you like):</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Bear Form</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="18" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
         <is>
           <t>Click-cast / mouseover (raid frames, not keys):</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Lifebloom, Regrowth, Rejuvenation, Swiftmend</t>
         </is>
@@ -1552,194 +1535,194 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Expunge</t>
+          <t>Obsidian Scales</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>Dispel / CC</t>
+          <t>Defensive</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Obsidian Scales</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>Defensive</t>
+          <t>Zephyr</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Defensive (major)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Zephyr</t>
+          <t>Sleep Walk</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>Defensive (major)</t>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Sleep Walk</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Breath of Eons</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Big cooldown</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Breath of Eons</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>Big cooldown</t>
+          <t>Verdant Embrace</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>Self-heal</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Verdant Embrace</t>
+          <t>Living Flame</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>Self-heal</t>
+          <t>Heal (out of combat)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Living Flame</t>
+          <t>Recuperate</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>Heal (out of combat)</t>
+          <t>Sustain / HoT</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>Shift+Q</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Recuperate</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>Sustain / HoT</t>
+          <t>Deep Breath</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Movement</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Shift+Q</t>
+          <t>Shift+4</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Deep Breath</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>Movement</t>
+          <t>Upheaval</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Spender</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Shift+4</t>
+          <t>Shift+F</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Upheaval</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>Spender</t>
+          <t>Time Skip</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Shift+F</t>
+          <t>Shift+X</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Time Skip</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
+          <t>Cauterizing Flame</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Shift+X</t>
+          <t>Shift+C</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -1747,7 +1730,7 @@
           <t>Landslide</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -1761,10 +1744,10 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Cauterizing Flame</t>
-        </is>
-      </c>
-      <c r="C23" s="13" t="inlineStr">
+          <t>Expunge</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -1979,194 +1962,194 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Expunge</t>
+          <t>Obsidian Scales</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>Dispel / CC</t>
+          <t>Defensive</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Obsidian Scales</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>Defensive</t>
+          <t>Zephyr</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Defensive (major)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Zephyr</t>
+          <t>Sleep Walk</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Defensive (major)</t>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Sleep Walk</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Dragonrage</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Big cooldown</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Dragonrage</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="inlineStr">
-        <is>
-          <t>Big cooldown</t>
+          <t>Verdant Embrace</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>Self-heal</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Verdant Embrace</t>
+          <t>Living Flame</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>Self-heal</t>
+          <t>Heal (out of combat)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Living Flame</t>
+          <t>Recuperate</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>Heal (out of combat)</t>
+          <t>Sustain / HoT</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>Shift+Q</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Recuperate</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>Sustain / HoT</t>
+          <t>Deep Breath</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Movement</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Shift+Q</t>
+          <t>Shift+2</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Deep Breath</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Movement</t>
+          <t>Azure Sweep</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Rotation</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Shift+2</t>
+          <t>Shift+4</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Azure Sweep</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>Rotation</t>
+          <t>Pyre</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Spender</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Shift+4</t>
+          <t>Shift+X</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Pyre</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>Spender</t>
+          <t>Cauterizing Flame</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Shift+X</t>
+          <t>Shift+C</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -2174,7 +2157,7 @@
           <t>Landslide</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -2188,10 +2171,10 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Cauterizing Flame</t>
-        </is>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
+          <t>Expunge</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -2389,160 +2372,160 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Expunge</t>
+          <t>Obsidian Scales</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>Dispel / CC</t>
+          <t>Defensive</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Obsidian Scales</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>Defensive</t>
+          <t>Zephyr</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Defensive (major)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Zephyr</t>
+          <t>Sleep Walk</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>Defensive (major)</t>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Sleep Walk</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Dream Flight</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Big cooldown</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Dream Flight</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>Big cooldown</t>
+          <t>Verdant Embrace</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>Self-heal</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Verdant Embrace</t>
+          <t>Living Flame</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>Self-heal</t>
+          <t>Heal (out of combat)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Living Flame</t>
+          <t>Recuperate</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>Heal (out of combat)</t>
+          <t>Sustain / HoT</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>Shift+Q</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Recuperate</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>Sustain / HoT</t>
+          <t>Deep Breath</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Movement</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Shift+Q</t>
+          <t>Shift+X</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Deep Breath</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>Movement</t>
+          <t>Cauterizing Flame</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Shift+X</t>
+          <t>Shift+C</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -2550,7 +2533,7 @@
           <t>Landslide</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -2564,10 +2547,10 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Cauterizing Flame</t>
-        </is>
-      </c>
-      <c r="C19" s="13" t="inlineStr">
+          <t>Expunge</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -2870,7 +2853,7 @@
           <t>Roar of Sacrifice</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -2887,7 +2870,7 @@
           <t>Survival of the Fittest</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -2904,7 +2887,7 @@
           <t>Aspect of the Turtle</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>Defensive (major)</t>
         </is>
@@ -2921,7 +2904,7 @@
           <t>Tranquilizing Shot</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -3074,7 +3057,7 @@
           <t>Binding Shot</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -3091,7 +3074,7 @@
           <t>Intimidation</t>
         </is>
       </c>
-      <c r="C24" s="13" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -3108,7 +3091,7 @@
           <t>Freezing Trap</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -3176,7 +3159,7 @@
           <t>Concussive Shot</t>
         </is>
       </c>
-      <c r="C29" s="13" t="inlineStr">
+      <c r="C29" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -3193,7 +3176,7 @@
           <t>Bursting Shot</t>
         </is>
       </c>
-      <c r="C30" s="13" t="inlineStr">
+      <c r="C30" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -3210,7 +3193,7 @@
           <t>Scatter Shot</t>
         </is>
       </c>
-      <c r="C31" s="13" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -3416,7 +3399,7 @@
           <t>Roar of Sacrifice</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -3433,7 +3416,7 @@
           <t>Survival of the Fittest</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -3450,7 +3433,7 @@
           <t>Aspect of the Turtle</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>Defensive (major)</t>
         </is>
@@ -3467,7 +3450,7 @@
           <t>Tranquilizing Shot</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -3688,7 +3671,7 @@
           <t>Binding Shot</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -3705,7 +3688,7 @@
           <t>Intimidation</t>
         </is>
       </c>
-      <c r="C28" s="13" t="inlineStr">
+      <c r="C28" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -3722,7 +3705,7 @@
           <t>Freezing Trap</t>
         </is>
       </c>
-      <c r="C29" s="13" t="inlineStr">
+      <c r="C29" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -3790,7 +3773,7 @@
           <t>Concussive Shot</t>
         </is>
       </c>
-      <c r="C33" s="13" t="inlineStr">
+      <c r="C33" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -3807,7 +3790,7 @@
           <t>Bursting Shot</t>
         </is>
       </c>
-      <c r="C34" s="13" t="inlineStr">
+      <c r="C34" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -3824,7 +3807,7 @@
           <t>Scatter Shot</t>
         </is>
       </c>
-      <c r="C35" s="13" t="inlineStr">
+      <c r="C35" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -4030,7 +4013,7 @@
           <t>Roar of Sacrifice</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -4047,7 +4030,7 @@
           <t>Survival of the Fittest</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -4064,7 +4047,7 @@
           <t>Aspect of the Turtle</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>Defensive (major)</t>
         </is>
@@ -4081,7 +4064,7 @@
           <t>Tranquilizing Shot</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -4268,7 +4251,7 @@
           <t>Binding Shot</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -4285,7 +4268,7 @@
           <t>Intimidation</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -4302,7 +4285,7 @@
           <t>Freezing Trap</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -4353,7 +4336,7 @@
           <t>Concussive Shot</t>
         </is>
       </c>
-      <c r="C30" s="13" t="inlineStr">
+      <c r="C30" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -4370,7 +4353,7 @@
           <t>Bursting Shot</t>
         </is>
       </c>
-      <c r="C31" s="13" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -4387,7 +4370,7 @@
           <t>Scatter Shot</t>
         </is>
       </c>
-      <c r="C32" s="13" t="inlineStr">
+      <c r="C32" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -4593,7 +4576,7 @@
           <t>Alter Time</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -4610,7 +4593,7 @@
           <t>Prismatic Barrier</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -4627,7 +4610,7 @@
           <t>Ice Block</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>Defensive (major)</t>
         </is>
@@ -4644,7 +4627,7 @@
           <t>Frost Nova</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -4797,7 +4780,7 @@
           <t>Remove Curse</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -4814,7 +4797,7 @@
           <t>Greater Invisibility</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -4831,7 +4814,7 @@
           <t>Ring of Frost</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -4848,7 +4831,7 @@
           <t>Polymorph</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -4882,7 +4865,7 @@
           <t>Dragon's Breath</t>
         </is>
       </c>
-      <c r="C28" s="13" t="inlineStr">
+      <c r="C28" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -4899,7 +4882,7 @@
           <t>Mirror Image</t>
         </is>
       </c>
-      <c r="C29" s="14" t="inlineStr">
+      <c r="C29" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -4916,7 +4899,7 @@
           <t>Spellsteal</t>
         </is>
       </c>
-      <c r="C30" s="13" t="inlineStr">
+      <c r="C30" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -5122,7 +5105,7 @@
           <t>Alter Time</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -5139,7 +5122,7 @@
           <t>Blazing Barrier</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -5156,7 +5139,7 @@
           <t>Ice Block</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>Defensive (major)</t>
         </is>
@@ -5173,7 +5156,7 @@
           <t>Frost Nova</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -5309,7 +5292,7 @@
           <t>Remove Curse</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -5326,7 +5309,7 @@
           <t>Greater Invisibility</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -5343,7 +5326,7 @@
           <t>Ring of Frost</t>
         </is>
       </c>
-      <c r="C24" s="13" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -5360,7 +5343,7 @@
           <t>Polymorph</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -5377,7 +5360,7 @@
           <t>Dragon's Breath</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -5394,7 +5377,7 @@
           <t>Cauterize</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -5411,7 +5394,7 @@
           <t>Mirror Image</t>
         </is>
       </c>
-      <c r="C28" s="14" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -5428,7 +5411,7 @@
           <t>Spellsteal</t>
         </is>
       </c>
-      <c r="C29" s="13" t="inlineStr">
+      <c r="C29" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -5634,7 +5617,7 @@
           <t>Alter Time</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -5651,7 +5634,7 @@
           <t>Ice Barrier</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -5668,7 +5651,7 @@
           <t>Ice Block</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>Defensive (major)</t>
         </is>
@@ -5685,7 +5668,7 @@
           <t>Frost Nova</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -5821,7 +5804,7 @@
           <t>Remove Curse</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -5838,7 +5821,7 @@
           <t>Greater Invisibility</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -5855,7 +5838,7 @@
           <t>Ring of Frost</t>
         </is>
       </c>
-      <c r="C24" s="13" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -5872,7 +5855,7 @@
           <t>Polymorph</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -5889,7 +5872,7 @@
           <t>Dragon's Breath</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -5906,7 +5889,7 @@
           <t>Mirror Image</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -5923,7 +5906,7 @@
           <t>Spellsteal</t>
         </is>
       </c>
-      <c r="C28" s="13" t="inlineStr">
+      <c r="C28" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -6109,12 +6092,12 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Death Grip</t>
+          <t>Anti-Magic Zone</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>Dispel / CC</t>
+          <t>Defensive</t>
         </is>
       </c>
     </row>
@@ -6129,7 +6112,7 @@
           <t>Lichborne</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -6146,7 +6129,7 @@
           <t>Icebound Fortitude</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>Defensive (major)</t>
         </is>
@@ -6163,7 +6146,7 @@
           <t>Vampiric Blood</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -6313,10 +6296,10 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Gorefiend's Grasp</t>
-        </is>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
+          <t>Chains of Ice</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -6325,32 +6308,32 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Shift+Z</t>
+          <t>Shift+C</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Anti-Magic Zone</t>
+          <t>Gorefiend's Grasp</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Shift+C</t>
+          <t>Shift+V</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Asphyxiate</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
+          <t>Death Grip</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -6359,15 +6342,15 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Shift+V</t>
+          <t>Ctrl+X</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Chains of Ice</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
+          <t>Strangulate</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -6381,10 +6364,10 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Strangulate</t>
-        </is>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
+          <t>Asphyxiate</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -6556,7 +6539,7 @@
           <t>Purifying Brew</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -6573,7 +6556,7 @@
           <t>Celestial Brew</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -6590,7 +6573,7 @@
           <t>Fortifying Brew</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Defensive (major)</t>
         </is>
@@ -6607,7 +6590,7 @@
           <t>Paralysis</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -6726,7 +6709,7 @@
           <t>Leg Sweep</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -6907,160 +6890,160 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Paralysis</t>
+          <t>Life Cocoon</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>Dispel / CC</t>
+          <t>Defensive</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Life Cocoon</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>Defensive</t>
+          <t>Fortifying Brew</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Defensive (major)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Fortifying Brew</t>
+          <t>Detox</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>Defensive (major)</t>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Detox</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Revival</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>Big cooldown</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Revival</t>
+          <t>Invoke Chi-Ji, the Red Crane</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>Big cooldown</t>
+          <t>Cooldown</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Invoke Chi-Ji, the Red Crane</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>Cooldown</t>
+          <t>Vivify</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>Heal (out of combat)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Vivify</t>
+          <t>Recuperate</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>Heal (out of combat)</t>
+          <t>Sustain / HoT</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>Shift+Q</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Recuperate</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>Sustain / HoT</t>
+          <t>Transcendence: Transfer</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Movement</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Shift+Q</t>
+          <t>Shift+X</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Transcendence: Transfer</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Movement</t>
+          <t>Ring of Peace</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Shift+X</t>
+          <t>Shift+C</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -7068,7 +7051,7 @@
           <t>Leg Sweep</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -7082,10 +7065,10 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Ring of Peace</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
+          <t>Paralysis</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -7341,170 +7324,170 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Leg Sweep</t>
+          <t>Touch of Karma</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>Dispel / CC</t>
+          <t>Defensive</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Touch of Karma</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>Defensive</t>
+          <t>Fortifying Brew</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Defensive (major)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Fortifying Brew</t>
+          <t>Paralysis</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>Defensive (major)</t>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Paralysis</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Invoke Xuen, the White Tiger</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Big cooldown</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Invoke Xuen, the White Tiger</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>Big cooldown</t>
+          <t>Expel Harm</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>Self-heal</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Expel Harm</t>
+          <t>Vivify</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>Self-heal</t>
+          <t>Heal (out of combat)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Vivify</t>
+          <t>Recuperate</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>Heal (out of combat)</t>
+          <t>Sustain / HoT</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>Shift+Q</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Recuperate</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>Sustain / HoT</t>
+          <t>Chi Torpedo</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Movement</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Shift+Q</t>
+          <t>Shift+2</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Chi Torpedo</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>Movement</t>
+          <t>Spinning Crane Kick</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Rotation</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Shift+2</t>
+          <t>Shift+V</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Spinning Crane Kick</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>Rotation</t>
+          <t>Leg Sweep</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
@@ -7654,12 +7637,12 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Cleanse Toxins</t>
+          <t>Blessing of Protection</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>Dispel / CC</t>
+          <t>Defensive</t>
         </is>
       </c>
     </row>
@@ -7674,7 +7657,7 @@
           <t>Divine Shield</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -7691,7 +7674,7 @@
           <t>Divine Protection</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -7708,7 +7691,7 @@
           <t>Cleanse</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -7824,10 +7807,10 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Blinding Light</t>
-        </is>
-      </c>
-      <c r="C17" s="13" t="inlineStr">
+          <t>Hammer of Justice</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -7841,10 +7824,10 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Blessing of Protection</t>
-        </is>
-      </c>
-      <c r="C18" s="14" t="inlineStr">
+          <t>Blessing of Sacrifice</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -7858,12 +7841,12 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Blessing of Sacrifice</t>
+          <t>Blinding Light</t>
         </is>
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
@@ -7875,10 +7858,10 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Hammer of Justice</t>
-        </is>
-      </c>
-      <c r="C20" s="13" t="inlineStr">
+          <t>Cleanse Toxins</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -7929,7 +7912,7 @@
           <t>Turn Evil</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -7946,7 +7929,7 @@
           <t>Blessing of Spellwarding</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -7963,7 +7946,7 @@
           <t>Blessing of Freedom</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -7980,7 +7963,7 @@
           <t>Repentance</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -8198,7 +8181,7 @@
           <t>Shield of the Righteous</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -8215,7 +8198,7 @@
           <t>Divine Shield</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -8232,7 +8215,7 @@
           <t>Guardian of Ancient Kings</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>Defensive (major)</t>
         </is>
@@ -8249,7 +8232,7 @@
           <t>Cleanse</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -8385,7 +8368,7 @@
           <t>Hammer of Justice</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -8402,7 +8385,7 @@
           <t>Ardent Defender</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -8419,7 +8402,7 @@
           <t>Divine Protection</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -8436,7 +8419,7 @@
           <t>Cleanse Toxins</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -8487,7 +8470,7 @@
           <t>Blessing of Sacrifice</t>
         </is>
       </c>
-      <c r="C28" s="14" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -8504,7 +8487,7 @@
           <t>Blessing of Protection</t>
         </is>
       </c>
-      <c r="C29" s="14" t="inlineStr">
+      <c r="C29" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -8521,7 +8504,7 @@
           <t>Holy Bulwark</t>
         </is>
       </c>
-      <c r="C30" s="14" t="inlineStr">
+      <c r="C30" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -8538,7 +8521,7 @@
           <t>Blinding Light</t>
         </is>
       </c>
-      <c r="C31" s="13" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -8741,12 +8724,12 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Cleanse Toxins</t>
+          <t>Blessing of Protection</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>Dispel / CC</t>
+          <t>Defensive</t>
         </is>
       </c>
     </row>
@@ -8761,7 +8744,7 @@
           <t>Divine Shield</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -8778,7 +8761,7 @@
           <t>Divine Protection</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -8795,7 +8778,7 @@
           <t>Cleanse</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -8928,10 +8911,10 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Blinding Light</t>
-        </is>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
+          <t>Hammer of Justice</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -8945,10 +8928,10 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Blessing of Protection</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="inlineStr">
+          <t>Blessing of Sacrifice</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -8962,12 +8945,12 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Blessing of Sacrifice</t>
+          <t>Blinding Light</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
@@ -8979,10 +8962,10 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Hammer of Justice</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
+          <t>Cleanse Toxins</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -9033,7 +9016,7 @@
           <t>Turn Evil</t>
         </is>
       </c>
-      <c r="C28" s="13" t="inlineStr">
+      <c r="C28" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -9050,7 +9033,7 @@
           <t>Blessing of Spellwarding</t>
         </is>
       </c>
-      <c r="C29" s="14" t="inlineStr">
+      <c r="C29" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -9067,7 +9050,7 @@
           <t>Blessing of Freedom</t>
         </is>
       </c>
-      <c r="C30" s="13" t="inlineStr">
+      <c r="C30" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -9084,7 +9067,7 @@
           <t>Repentance</t>
         </is>
       </c>
-      <c r="C31" s="13" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -9273,7 +9256,7 @@
           <t>Pain Suppression</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -9290,7 +9273,7 @@
           <t>Power Word: Shield</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -9307,7 +9290,7 @@
           <t>Power Word: Barrier</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>Defensive (major)</t>
         </is>
@@ -9324,7 +9307,7 @@
           <t>Psychic Scream</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -9443,7 +9426,7 @@
           <t>Mass Dispel</t>
         </is>
       </c>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -9460,7 +9443,7 @@
           <t>Dispel Magic</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -9477,7 +9460,7 @@
           <t>Purify</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -9528,7 +9511,7 @@
           <t>Shackle Horror</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -9733,131 +9716,131 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Purify</t>
+          <t>Guardian Spirit</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>Dispel / CC</t>
+          <t>Defensive (major)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Guardian Spirit</t>
+          <t>Psychic Scream</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>Defensive (major)</t>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Psychic Scream</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Apotheosis</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Big cooldown</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Apotheosis</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>Big cooldown</t>
+          <t>Desperate Prayer</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>Self-heal</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Desperate Prayer</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>Self-heal</t>
+          <t>Divine Hymn</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Cooldown</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Divine Hymn</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>Cooldown</t>
+          <t>Recuperate</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>Sustain / HoT</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>Shift+F</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Recuperate</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>Sustain / HoT</t>
+          <t>Mind Control</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Shift+F</t>
+          <t>Shift+R</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Mind Control</t>
+          <t>Leap of Faith</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -9869,24 +9852,24 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Shift+R</t>
+          <t>Shift+X</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Leap of Faith</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
+          <t>Mass Dispel</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Shift+X</t>
+          <t>Shift+C</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -9894,7 +9877,7 @@
           <t>Dispel Magic</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -9903,15 +9886,15 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Shift+C</t>
+          <t>Shift+V</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Shackle Horror</t>
-        </is>
-      </c>
-      <c r="C20" s="13" t="inlineStr">
+          <t>Purify</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -9920,63 +9903,63 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Shift+V</t>
+          <t>Shift+F1</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Mass Dispel</t>
-        </is>
-      </c>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Power Infusion</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Big cooldown</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Shift+F1</t>
+          <t>Shift+F3</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Power Infusion</t>
+          <t>Holy Word: Salvation</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>Big cooldown</t>
+          <t>Cooldown</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Shift+F3</t>
+          <t>Ctrl+F</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Holy Word: Salvation</t>
-        </is>
-      </c>
-      <c r="C23" s="15" t="inlineStr">
-        <is>
-          <t>Cooldown</t>
+          <t>Power Word: Life</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+F</t>
+          <t>Ctrl+R</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Power Word: Life</t>
+          <t>Levitate</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
@@ -9988,12 +9971,12 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+R</t>
+          <t>Ctrl+X</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Levitate</t>
+          <t>Power Word: Fortitude</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
@@ -10005,17 +9988,17 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+X</t>
+          <t>Ctrl+V</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Power Word: Fortitude</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
+          <t>Shackle Horror</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
@@ -10223,148 +10206,148 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Purify Disease</t>
+          <t>Power Word: Shield</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>Dispel / CC</t>
+          <t>Defensive</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Power Word: Shield</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>Defensive</t>
+          <t>Dispersion</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Defensive (major)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Dispersion</t>
+          <t>Psychic Scream</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>Defensive (major)</t>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Psychic Scream</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Voidform</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Big cooldown</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Voidform</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>Big cooldown</t>
+          <t>Desperate Prayer</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>Self-heal</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Desperate Prayer</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>Self-heal</t>
+          <t>Void Torrent</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Cooldown</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Void Torrent</t>
-        </is>
-      </c>
-      <c r="C17" s="15" t="inlineStr">
-        <is>
-          <t>Cooldown</t>
+          <t>Recuperate</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>Sustain / HoT</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>Shift+1</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Recuperate</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>Sustain / HoT</t>
+          <t>Mind Flay</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Rotation</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Shift+1</t>
+          <t>Shift+2</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Mind Flay</t>
+          <t>Tentacle Slam</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
@@ -10376,12 +10359,12 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Shift+2</t>
+          <t>Shift+3</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Tentacle Slam</t>
+          <t>Void Volley</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
@@ -10393,29 +10376,29 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Shift+3</t>
+          <t>Shift+F</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Void Volley</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>Rotation</t>
+          <t>Leap of Faith</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Shift+F</t>
+          <t>Shift+R</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Leap of Faith</t>
+          <t>Levitate</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
@@ -10427,24 +10410,24 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Shift+R</t>
+          <t>Shift+X</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Levitate</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
+          <t>Mass Dispel</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Shift+X</t>
+          <t>Shift+C</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -10452,7 +10435,7 @@
           <t>Dispel Magic</t>
         </is>
       </c>
-      <c r="C24" s="13" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -10461,15 +10444,15 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Shift+C</t>
+          <t>Shift+V</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Shackle Horror</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
+          <t>Purify Disease</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -10478,63 +10461,63 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Shift+V</t>
+          <t>Shift+F1</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Mass Dispel</t>
-        </is>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Power Infusion</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>Big cooldown</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Shift+F1</t>
+          <t>Shift+F3</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Power Infusion</t>
+          <t>Vampiric Embrace</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>Big cooldown</t>
+          <t>Cooldown</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Shift+F3</t>
+          <t>Ctrl+F</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Vampiric Embrace</t>
-        </is>
-      </c>
-      <c r="C28" s="15" t="inlineStr">
-        <is>
-          <t>Cooldown</t>
+          <t>Power Word: Fortitude</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+F</t>
+          <t>Ctrl+R</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Power Word: Fortitude</t>
+          <t>Shadowform</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
@@ -10546,17 +10529,17 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+R</t>
+          <t>Ctrl+V</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Shadowform</t>
-        </is>
-      </c>
-      <c r="C30" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
+          <t>Shackle Horror</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
@@ -10740,12 +10723,12 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Shiv</t>
+          <t>Evasion</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>Dispel / CC</t>
+          <t>Defensive</t>
         </is>
       </c>
     </row>
@@ -10760,7 +10743,7 @@
           <t>Feint</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -10777,7 +10760,7 @@
           <t>Cloak of Shadows</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>Defensive (major)</t>
         </is>
@@ -10794,7 +10777,7 @@
           <t>Blind</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -10944,10 +10927,10 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Cheap Shot</t>
-        </is>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
+          <t>Kidney Shot</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -10961,12 +10944,12 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Evasion</t>
+          <t>Cheap Shot</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>Defensive (major)</t>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
@@ -10978,10 +10961,10 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Kidney Shot</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
+          <t>Shiv</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -11015,7 +10998,7 @@
           <t>Gouge</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -11032,7 +11015,7 @@
           <t>Sap</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -11218,12 +11201,12 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Chains of Ice</t>
+          <t>Anti-Magic Zone</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>Dispel / CC</t>
+          <t>Defensive</t>
         </is>
       </c>
     </row>
@@ -11238,7 +11221,7 @@
           <t>Lichborne</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -11255,7 +11238,7 @@
           <t>Icebound Fortitude</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>Defensive (major)</t>
         </is>
@@ -11272,7 +11255,7 @@
           <t>Death Grip</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -11439,10 +11422,10 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Strangulate</t>
-        </is>
-      </c>
-      <c r="C23" s="13" t="inlineStr">
+          <t>Blinding Sleet</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -11451,17 +11434,17 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Shift+Z</t>
+          <t>Shift+C</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Anti-Magic Zone</t>
+          <t>Strangulate</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
@@ -11473,10 +11456,10 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Blinding Sleet</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
+          <t>Chains of Ice</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -11713,12 +11696,12 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Shiv</t>
+          <t>Evasion</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>Dispel / CC</t>
+          <t>Defensive</t>
         </is>
       </c>
     </row>
@@ -11733,7 +11716,7 @@
           <t>Feint</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -11750,7 +11733,7 @@
           <t>Cloak of Shadows</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>Defensive (major)</t>
         </is>
@@ -11767,7 +11750,7 @@
           <t>Blind</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -11900,10 +11883,10 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Cheap Shot</t>
-        </is>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
+          <t>Kidney Shot</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -11917,12 +11900,12 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Evasion</t>
+          <t>Cheap Shot</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>Defensive (major)</t>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
@@ -11934,10 +11917,10 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Kidney Shot</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
+          <t>Shiv</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -11988,7 +11971,7 @@
           <t>Gouge</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -12005,7 +11988,7 @@
           <t>Sap</t>
         </is>
       </c>
-      <c r="C28" s="13" t="inlineStr">
+      <c r="C28" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -12191,12 +12174,12 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Shiv</t>
+          <t>Evasion</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>Dispel / CC</t>
+          <t>Defensive</t>
         </is>
       </c>
     </row>
@@ -12211,7 +12194,7 @@
           <t>Feint</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -12228,7 +12211,7 @@
           <t>Cloak of Shadows</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>Defensive (major)</t>
         </is>
@@ -12245,7 +12228,7 @@
           <t>Blind</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -12412,10 +12395,10 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Cheap Shot</t>
-        </is>
-      </c>
-      <c r="C23" s="13" t="inlineStr">
+          <t>Kidney Shot</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -12429,12 +12412,12 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Evasion</t>
+          <t>Cheap Shot</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Defensive (major)</t>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
@@ -12446,10 +12429,10 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Kidney Shot</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
+          <t>Shiv</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -12483,7 +12466,7 @@
           <t>Gouge</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -12500,7 +12483,7 @@
           <t>Sap</t>
         </is>
       </c>
-      <c r="C28" s="13" t="inlineStr">
+      <c r="C28" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -12681,199 +12664,199 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Purge</t>
+          <t>Earth Elemental</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>Dispel / CC</t>
+          <t>Defensive</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Earth Elemental</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>Defensive</t>
+          <t>Astral Shift</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Defensive (major)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Astral Shift</t>
+          <t>Hex</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Defensive (major)</t>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Hex</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Stormkeeper</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Big cooldown</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Stormkeeper</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="inlineStr">
-        <is>
-          <t>Big cooldown</t>
+          <t>Healing Surge</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>Self-heal</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Healing Surge</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>Self-heal</t>
+          <t>Ascendance</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>Cooldown</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Ascendance</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="inlineStr">
-        <is>
-          <t>Cooldown</t>
+          <t>Recuperate</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>Sustain / HoT</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>Shift+Q</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Recuperate</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>Sustain / HoT</t>
+          <t>Ghost Wolf</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Movement</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Shift+Q</t>
+          <t>Shift+1</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Ghost Wolf</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Movement</t>
+          <t>Chain Lightning</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Rotation</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Shift+1</t>
+          <t>Shift+4</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Chain Lightning</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>Rotation</t>
+          <t>Earthquake</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Spender</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Shift+4</t>
+          <t>Shift+F</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Earthquake</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>Spender</t>
+          <t>Thunderstorm</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Shift+F</t>
+          <t>Shift+R</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Thunderstorm</t>
+          <t>Tremor Totem</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
@@ -12885,24 +12868,24 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Shift+R</t>
+          <t>Shift+X</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Tremor Totem</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
+          <t>Capacitor Totem</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Shift+X</t>
+          <t>Shift+C</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -12910,7 +12893,7 @@
           <t>Cleanse Spirit</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -12924,10 +12907,10 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Capacitor Totem</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
+          <t>Purge</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -12995,7 +12978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13176,17 +13159,17 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Purge</t>
+          <t>Earth Elemental</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>Dispel / CC</t>
+          <t>Defensive</t>
         </is>
       </c>
     </row>
@@ -13201,7 +13184,7 @@
           <t>Astral Shift</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>Defensive (major)</t>
         </is>
@@ -13218,7 +13201,7 @@
           <t>Hex</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -13397,7 +13380,7 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Shift+V</t>
+          <t>Shift+X</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -13405,7 +13388,7 @@
           <t>Capacitor Totem</t>
         </is>
       </c>
-      <c r="C24" s="13" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -13414,29 +13397,29 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Shift+F1</t>
+          <t>Shift+V</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Ascendance</t>
-        </is>
-      </c>
-      <c r="C25" s="15" t="inlineStr">
-        <is>
-          <t>Cooldown</t>
+          <t>Purge</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Shift+F2</t>
+          <t>Shift+F1</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Heroism</t>
+          <t>Ascendance</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
@@ -13448,12 +13431,12 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Shift+F3</t>
+          <t>Shift+F2</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Bloodlust</t>
+          <t>Heroism</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
@@ -13465,15 +13448,32 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
+          <t>Shift+F3</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Bloodlust</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>Cooldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
           <t>Ctrl+Q</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>Ghost Wolf</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>Movement</t>
         </is>
@@ -13490,7 +13490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13654,17 +13654,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Purge</t>
+          <t>Earth Elemental</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>Dispel / CC</t>
+          <t>Defensive</t>
         </is>
       </c>
     </row>
@@ -13679,7 +13679,7 @@
           <t>Astral Shift</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Defensive (major)</t>
         </is>
@@ -13696,7 +13696,7 @@
           <t>Hex</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -13829,10 +13829,10 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Capacitor Totem</t>
-        </is>
-      </c>
-      <c r="C20" s="13" t="inlineStr">
+          <t>Purify Spirit</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -13841,15 +13841,15 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Shift+V</t>
+          <t>Shift+C</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Purify Spirit</t>
-        </is>
-      </c>
-      <c r="C21" s="13" t="inlineStr">
+          <t>Capacitor Totem</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -13858,29 +13858,29 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Shift+F1</t>
+          <t>Shift+V</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Bloodlust</t>
-        </is>
-      </c>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>Cooldown</t>
+          <t>Purge</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Shift+F3</t>
+          <t>Shift+F1</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Heroism</t>
+          <t>Bloodlust</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
@@ -13892,27 +13892,44 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
+          <t>Shift+F3</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Heroism</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Cooldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
           <t>Ctrl+F</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>Nature's Swiftness</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>Utility</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="18" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>Click-cast / mouseover (raid frames, not keys):</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Healing Wave, Riptide, Unleash Life</t>
         </is>
@@ -14110,15 +14127,15 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Fear</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
+          <t>Dark Pact</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -14127,165 +14144,165 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Dark Pact</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>Defensive</t>
+          <t>Unending Resolve</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Defensive (major)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Unending Resolve</t>
+          <t>Fear</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>Defensive (major)</t>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Mortal Coil</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Summon Darkglare</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Big cooldown</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Summon Darkglare</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>Big cooldown</t>
+          <t>Drain Life</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>Self-heal</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Drain Life</t>
+          <t>Healthstone</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>Self-heal</t>
+          <t>Heal (out of combat)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Healthstone</t>
+          <t>Recuperate</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>Heal (out of combat)</t>
+          <t>Sustain / HoT</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>Shift+E</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Recuperate</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>Sustain / HoT</t>
+          <t>Call Felhunter</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Interrupt</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Shift+E</t>
+          <t>Shift+Q</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Call Felhunter</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Interrupt</t>
+          <t>Demonic Circle: Teleport</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Movement</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Shift+Q</t>
+          <t>Shift+1</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Demonic Circle: Teleport</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Movement</t>
+          <t>Haunt</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Rotation</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Shift+1</t>
+          <t>Shift+2</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Haunt</t>
+          <t>Drain Soul</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
@@ -14297,46 +14314,46 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Shift+2</t>
+          <t>Shift+4</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Drain Soul</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>Rotation</t>
+          <t>Seed of Corruption</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>Spender</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Shift+4</t>
+          <t>Shift+F</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Seed of Corruption</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>Spender</t>
+          <t>Command Demon</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Shift+F</t>
+          <t>Shift+R</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Command Demon</t>
+          <t>Create Healthstone</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
@@ -14348,24 +14365,24 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Shift+R</t>
+          <t>Shift+X</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Create Healthstone</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
+          <t>Howl of Terror</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Shift+X</t>
+          <t>Shift+C</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -14373,7 +14390,7 @@
           <t>Banish</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -14387,10 +14404,10 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Howl of Terror</t>
-        </is>
-      </c>
-      <c r="C27" s="13" t="inlineStr">
+          <t>Mortal Coil</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -14622,15 +14639,15 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Fear</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
+          <t>Dark Pact</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -14639,165 +14656,165 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Dark Pact</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>Defensive</t>
+          <t>Unending Resolve</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Defensive (major)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Unending Resolve</t>
+          <t>Fear</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>Defensive (major)</t>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Mortal Coil</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Summon Demonic Tyrant</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Big cooldown</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Summon Demonic Tyrant</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>Big cooldown</t>
+          <t>Drain Life</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>Self-heal</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Drain Life</t>
+          <t>Healthstone</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>Self-heal</t>
+          <t>Heal (out of combat)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Healthstone</t>
+          <t>Recuperate</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>Heal (out of combat)</t>
+          <t>Sustain / HoT</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>Shift+Q</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Recuperate</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>Sustain / HoT</t>
+          <t>Demonic Circle: Teleport</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Movement</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Shift+Q</t>
+          <t>Shift+4</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Demonic Circle: Teleport</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>Movement</t>
+          <t>Implosion</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Spender</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Shift+4</t>
+          <t>Shift+F</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Implosion</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>Spender</t>
+          <t>Command Demon</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Shift+F</t>
+          <t>Shift+R</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Command Demon</t>
+          <t>Create Healthstone</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
@@ -14809,24 +14826,24 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Shift+R</t>
+          <t>Shift+X</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Create Healthstone</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
+          <t>Howl of Terror</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Shift+X</t>
+          <t>Shift+C</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -14834,7 +14851,7 @@
           <t>Banish</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -14848,10 +14865,10 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Howl of Terror</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
+          <t>Mortal Coil</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -15066,15 +15083,15 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Fear</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
+          <t>Dark Pact</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -15083,165 +15100,165 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Dark Pact</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>Defensive</t>
+          <t>Unending Resolve</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Defensive (major)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Unending Resolve</t>
+          <t>Fear</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>Defensive (major)</t>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Mortal Coil</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Summon Infernal</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Big cooldown</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Summon Infernal</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>Big cooldown</t>
+          <t>Drain Life</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>Self-heal</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Drain Life</t>
+          <t>Healthstone</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>Self-heal</t>
+          <t>Heal (out of combat)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Healthstone</t>
+          <t>Recuperate</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>Heal (out of combat)</t>
+          <t>Sustain / HoT</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>Shift+E</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Recuperate</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>Sustain / HoT</t>
+          <t>Call Felhunter</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Interrupt</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Shift+E</t>
+          <t>Shift+Q</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Call Felhunter</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Interrupt</t>
+          <t>Demonic Circle: Teleport</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Movement</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Shift+Q</t>
+          <t>Shift+1</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Demonic Circle: Teleport</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Movement</t>
+          <t>Soul Fire</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Rotation</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Shift+1</t>
+          <t>Shift+2</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Soul Fire</t>
+          <t>Cataclysm</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
@@ -15253,12 +15270,12 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Shift+2</t>
+          <t>Shift+3</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Cataclysm</t>
+          <t>Channel Demonfire</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
@@ -15270,63 +15287,63 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Shift+3</t>
+          <t>Shift+4</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Channel Demonfire</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>Rotation</t>
+          <t>Rain of Fire</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>Spender</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Shift+4</t>
+          <t>Shift+5</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Rain of Fire</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>Spender</t>
+          <t>Dimensional Rift</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Rotation</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Shift+5</t>
+          <t>Shift+F</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Dimensional Rift</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>Rotation</t>
+          <t>Command Demon</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Shift+F</t>
+          <t>Shift+R</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Command Demon</t>
+          <t>Create Healthstone</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
@@ -15338,24 +15355,24 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Shift+R</t>
+          <t>Shift+X</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Create Healthstone</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
+          <t>Howl of Terror</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Shift+X</t>
+          <t>Shift+C</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -15363,7 +15380,7 @@
           <t>Banish</t>
         </is>
       </c>
-      <c r="C28" s="13" t="inlineStr">
+      <c r="C28" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -15377,10 +15394,10 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Howl of Terror</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="inlineStr">
+          <t>Mortal Coil</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -15620,7 +15637,7 @@
           <t>Rallying Cry</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -15637,7 +15654,7 @@
           <t>Ignore Pain</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -15654,7 +15671,7 @@
           <t>Die by the Sword</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>Defensive (major)</t>
         </is>
@@ -15671,7 +15688,7 @@
           <t>Intimidating Shout</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -15841,7 +15858,7 @@
           <t>Storm Bolt</t>
         </is>
       </c>
-      <c r="C24" s="13" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -15858,7 +15875,7 @@
           <t>Intervene</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C25" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -15875,7 +15892,7 @@
           <t>Spell Reflection</t>
         </is>
       </c>
-      <c r="C26" s="14" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -15892,7 +15909,7 @@
           <t>Berserker Rage</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -16166,7 +16183,7 @@
           <t>Intervene</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -16183,7 +16200,7 @@
           <t>Rallying Cry</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -16200,7 +16217,7 @@
           <t>Enraged Regeneration</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>Defensive (major)</t>
         </is>
@@ -16217,7 +16234,7 @@
           <t>Intimidating Shout</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -16387,7 +16404,7 @@
           <t>Storm Bolt</t>
         </is>
       </c>
-      <c r="C24" s="13" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -16404,7 +16421,7 @@
           <t>Spell Reflection</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C25" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -16421,7 +16438,7 @@
           <t>Berserker Rage</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -16658,12 +16675,12 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Chains of Ice</t>
+          <t>Anti-Magic Zone</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>Dispel / CC</t>
+          <t>Defensive</t>
         </is>
       </c>
     </row>
@@ -16678,7 +16695,7 @@
           <t>Lichborne</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -16695,7 +16712,7 @@
           <t>Icebound Fortitude</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>Defensive (major)</t>
         </is>
@@ -16712,7 +16729,7 @@
           <t>Death Grip</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -16862,10 +16879,10 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Strangulate</t>
-        </is>
-      </c>
-      <c r="C23" s="13" t="inlineStr">
+          <t>Asphyxiate</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -16874,17 +16891,17 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Shift+Z</t>
+          <t>Shift+C</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Anti-Magic Zone</t>
+          <t>Strangulate</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
@@ -16896,10 +16913,10 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Asphyxiate</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
+          <t>Chains of Ice</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -17085,12 +17102,12 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Shockwave</t>
+          <t>Rallying Cry</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>Dispel / CC</t>
+          <t>Defensive</t>
         </is>
       </c>
     </row>
@@ -17105,7 +17122,7 @@
           <t>Ignore Pain</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -17122,7 +17139,7 @@
           <t>Shield Wall</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>Defensive (major)</t>
         </is>
@@ -17139,7 +17156,7 @@
           <t>Intimidating Shout</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -17306,12 +17323,12 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Rallying Cry</t>
+          <t>Shockwave</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
@@ -17326,7 +17343,7 @@
           <t>Shield Block</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -17343,7 +17360,7 @@
           <t>Spell Reflection</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C25" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -17360,7 +17377,7 @@
           <t>Berserker Rage</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -17496,7 +17513,7 @@
           <t>Intervene</t>
         </is>
       </c>
-      <c r="C34" s="14" t="inlineStr">
+      <c r="C34" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -17694,32 +17711,32 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Consume Magic</t>
+          <t>Blur</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>Dispel / CC</t>
+          <t>Defensive</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Blur</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
+          <t>Darkness</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -17728,63 +17745,63 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Darkness</t>
+          <t>Chaos Nova</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Chaos Nova</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Metamorphosis</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Big cooldown</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Metamorphosis</t>
+          <t>Reaver's Glaive</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>Big cooldown</t>
+          <t>Cooldown</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Reaver's Glaive</t>
+          <t>Essence Break</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -17796,63 +17813,63 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Essence Break</t>
-        </is>
-      </c>
-      <c r="C17" s="15" t="inlineStr">
-        <is>
-          <t>Cooldown</t>
+          <t>Recuperate</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>Sustain / HoT</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>Shift+Q</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Recuperate</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>Sustain / HoT</t>
+          <t>Vengeful Retreat</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Movement</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Shift+Q</t>
+          <t>Shift+1</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Vengeful Retreat</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>Movement</t>
+          <t>Immolation Aura</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Rotation</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Shift+1</t>
+          <t>Shift+2</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Immolation Aura</t>
+          <t>Eye Beam</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
@@ -17864,12 +17881,12 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Shift+2</t>
+          <t>Shift+3</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Eye Beam</t>
+          <t>Sigil of Doom</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
@@ -17881,12 +17898,12 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Shift+3</t>
+          <t>Shift+4</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Sigil of Doom</t>
+          <t>Blade Dance</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
@@ -17898,34 +17915,34 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Shift+4</t>
+          <t>Shift+F</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Blade Dance</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>Rotation</t>
+          <t>Glide</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Shift+F</t>
+          <t>Shift+X</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Glide</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
+          <t>Consume Magic</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
@@ -17940,7 +17957,7 @@
           <t>Sigil of Misery</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -17991,7 +18008,7 @@
           <t>Imprison</t>
         </is>
       </c>
-      <c r="C28" s="13" t="inlineStr">
+      <c r="C28" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -18003,6 +18020,518 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Ability</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>Disrupt</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Interrupt</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Infernal Strike</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Shear</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Rotation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Fracture</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Rotation</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Immolation Aura</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Rotation</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Soul Cleave</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Spender</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Sigil of Flame</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Rotation</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Torment</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>Taunt</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Spectral Sight</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Darkness</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Defensive</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Demon Spikes</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Defensive</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Fiery Brand</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Defensive (major)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Chaos Nova</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Sigil of Spite</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>Cooldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Recuperate</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>Sustain / HoT</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Shift+Q</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Vengeful Retreat</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Shift+4</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Spirit Bomb</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Spender</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Shift+F</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Glide</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Shift+X</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Sigil of Silence</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Shift+Z</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Fel Devastation</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Defensive</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Shift+C</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Metamorphosis (Vengeance)</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>Defensive (major)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Shift+V</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Sigil of Misery</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Shift+F1</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>The Hunt</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Big cooldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+Q</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Felblade</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+X</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Consume Magic</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+C</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Sigil of Chains</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+V</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Imprison</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+F1</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Soul Carver</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>Cooldown</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18041,7 +18570,7 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>Disrupt</t>
+          <t>Solar Beam</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
@@ -18058,7 +18587,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Infernal Strike</t>
+          <t>Wild Charge</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
@@ -18075,7 +18604,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Shear</t>
+          <t>Wrath</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
@@ -18092,7 +18621,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Fracture</t>
+          <t>Starfire</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
@@ -18109,7 +18638,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Immolation Aura</t>
+          <t>Moonfire</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -18126,7 +18655,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Soul Cleave</t>
+          <t>Starsurge</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -18143,7 +18672,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Sigil of Flame</t>
+          <t>Sunfire</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -18160,12 +18689,12 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Torment</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>Taunt</t>
+          <t>Rebirth</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
@@ -18177,160 +18706,160 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Spectral Sight</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
+          <t>Travel Form</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Mobility</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Sigil of Silence</t>
+          <t>Barkskin</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>Dispel / CC</t>
+          <t>Defensive</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Demon Spikes</t>
+          <t>Typhoon</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Fiery Brand</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>Defensive (major)</t>
+          <t>Celestial Alignment</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Big cooldown</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Chaos Nova</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Incarnation: Chosen of Elune</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Cooldown</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Sigil of Spite</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>Cooldown</t>
+          <t>Recuperate</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>Sustain / HoT</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>Shift+Q</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Recuperate</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>Sustain / HoT</t>
+          <t>Tiger Dash</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Movement</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Shift+Q</t>
+          <t>Shift+4</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Vengeful Retreat</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>Movement</t>
+          <t>Starfall</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Spender</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Shift+4</t>
+          <t>Shift+F</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Spirit Bomb</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>Spender</t>
+          <t>Innervate</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Shift+F</t>
+          <t>Shift+R</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Glide</t>
+          <t>Cat Form</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
@@ -18347,97 +18876,97 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Consume Magic</t>
-        </is>
-      </c>
-      <c r="C20" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Moonkin Form</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Shift+Z</t>
+          <t>Shift+C</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Darkness</t>
+          <t>Cyclone</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Shift+C</t>
+          <t>Shift+V</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Metamorphosis (Vengeance)</t>
+          <t>Mighty Bash</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Defensive (major)</t>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Shift+V</t>
+          <t>Ctrl+Q</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Sigil of Misery</t>
-        </is>
-      </c>
-      <c r="C23" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Dash</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Movement</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Shift+F1</t>
+          <t>Ctrl+F</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>The Hunt</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr">
-        <is>
-          <t>Big cooldown</t>
+          <t>Prowl</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+Q</t>
+          <t>Ctrl+R</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Felblade</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>Movement</t>
+          <t>Mark of the Wild</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
@@ -18449,10 +18978,10 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Sigil of Chains</t>
-        </is>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
+          <t>Soothe</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -18461,590 +18990,44 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+Z</t>
+          <t>Ctrl+C</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Fel Devastation</t>
+          <t>Remove Corruption</t>
         </is>
       </c>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+C</t>
+          <t>Ctrl+V</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Fel Eruption</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="inlineStr">
+          <t>Entangling Roots</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Ctrl+V</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>Imprison</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
-        </is>
-      </c>
-    </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Ctrl+F1</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Soul Carver</t>
-        </is>
-      </c>
-      <c r="C30" s="15" t="inlineStr">
-        <is>
-          <t>Cooldown</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Key</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>Ability</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>Solar Beam</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>Interrupt</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>Q</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Wild Charge</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>Movement</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Wrath</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>Rotation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Starfire</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>Rotation</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Moonfire</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>Rotation</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Starsurge</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Spender</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Sunfire</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>Rotation</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Rebirth</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Travel Form</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Mobility</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Mighty Bash</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Barkskin</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>Defensive</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Cyclone</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Typhoon</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Celestial Alignment</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>Big cooldown</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Incarnation: Chosen of Elune</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="inlineStr">
-        <is>
-          <t>Cooldown</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>F4</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Recuperate</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>Sustain / HoT</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Shift+Q</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Tiger Dash</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Movement</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Shift+4</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Starfall</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>Spender</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Shift+F</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Innervate</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Shift+R</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Cat Form</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Shift+X</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Moonkin Form</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Shift+C</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Soothe</t>
-        </is>
-      </c>
-      <c r="C23" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Shift+V</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Entangling Roots</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Ctrl+Q</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Dash</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>Movement</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Ctrl+F</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Prowl</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Ctrl+R</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Mark of the Wild</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Ctrl+X</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Ursol's Vortex</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Ctrl+V</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>Remove Corruption</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="A30" s="18" t="inlineStr">
         <is>
           <t>Situational (no fixed key — bind where you like):</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Bear Form</t>
         </is>
@@ -19061,7 +19044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19225,199 +19208,199 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Incapacitating Roar</t>
+          <t>Barkskin</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>Dispel / CC</t>
+          <t>Defensive</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Barkskin</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>Defensive</t>
+          <t>Survival Instincts</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Defensive (major)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Survival Instincts</t>
+          <t>Maim</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Defensive (major)</t>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Maim</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Berserk</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Big cooldown</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Berserk</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="inlineStr">
-        <is>
-          <t>Big cooldown</t>
+          <t>Frenzied Regeneration</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>Self-heal</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Frenzied Regeneration</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>Self-heal</t>
+          <t>Incarnation: Avatar of Ashamane</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>Cooldown</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Incarnation: Avatar of Ashamane</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="inlineStr">
-        <is>
-          <t>Cooldown</t>
+          <t>Recuperate</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>Sustain / HoT</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>Shift+Q</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Recuperate</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>Sustain / HoT</t>
+          <t>Stampeding Roar</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Movement</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Shift+Q</t>
+          <t>Shift+1</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Stampeding Roar</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Movement</t>
+          <t>Swipe</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Rotation</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Shift+1</t>
+          <t>Shift+4</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Swipe</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>Rotation</t>
+          <t>Primal Wrath</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Spender</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Shift+4</t>
+          <t>Shift+F</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Primal Wrath</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>Spender</t>
+          <t>Prowl</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Shift+F</t>
+          <t>Shift+R</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Prowl</t>
+          <t>Cat Form</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
@@ -19429,12 +19412,12 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Shift+R</t>
+          <t>Shift+X</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Cat Form</t>
+          <t>Moonkin Form</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
@@ -19446,32 +19429,32 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Shift+X</t>
+          <t>Shift+C</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Moonkin Form</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
+          <t>Cyclone</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Shift+C</t>
+          <t>Shift+V</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Entangling Roots</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
+          <t>Incapacitating Roar</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -19480,63 +19463,63 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Shift+V</t>
+          <t>Shift+F1</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Cyclone</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Tiger's Fury</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>Cooldown</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Shift+F1</t>
+          <t>Ctrl+Q</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Tiger's Fury</t>
-        </is>
-      </c>
-      <c r="C26" s="15" t="inlineStr">
-        <is>
-          <t>Cooldown</t>
+          <t>Dash</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Movement</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+Q</t>
+          <t>Ctrl+F</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Dash</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>Movement</t>
+          <t>Mark of the Wild</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+F</t>
+          <t>Ctrl+R</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Mark of the Wild</t>
+          <t>Revive</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
@@ -19548,24 +19531,24 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+R</t>
+          <t>Ctrl+X</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Revive</t>
-        </is>
-      </c>
-      <c r="C29" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
+          <t>Soothe</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+X</t>
+          <t>Ctrl+C</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -19573,7 +19556,7 @@
           <t>Remove Corruption</t>
         </is>
       </c>
-      <c r="C30" s="13" t="inlineStr">
+      <c r="C30" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -19582,44 +19565,27 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+C</t>
+          <t>Ctrl+V</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Ursol's Vortex</t>
-        </is>
-      </c>
-      <c r="C31" s="13" t="inlineStr">
+          <t>Entangling Roots</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>Ctrl+V</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Soothe</t>
-        </is>
-      </c>
-      <c r="C32" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="18" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="18" t="inlineStr">
         <is>
           <t>Situational (no fixed key — bind where you like):</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Bear Form</t>
         </is>
@@ -19808,7 +19774,7 @@
           <t>Ironfur</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -19825,7 +19791,7 @@
           <t>Barkskin</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -19842,7 +19808,7 @@
           <t>Survival Instincts</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>Defensive (major)</t>
         </is>
@@ -19859,7 +19825,7 @@
           <t>Typhoon</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -20029,7 +19995,7 @@
           <t>Bristling Fur</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
         </is>
@@ -20046,7 +20012,7 @@
           <t>Incapacitating Roar</t>
         </is>
       </c>
-      <c r="C24" s="13" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -20063,7 +20029,7 @@
           <t>Mighty Bash</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -20165,7 +20131,7 @@
           <t>Entangling Roots</t>
         </is>
       </c>
-      <c r="C31" s="13" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -20182,7 +20148,7 @@
           <t>Soothe</t>
         </is>
       </c>
-      <c r="C32" s="13" t="inlineStr">
+      <c r="C32" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -20199,7 +20165,7 @@
           <t>Cyclone</t>
         </is>
       </c>
-      <c r="C33" s="13" t="inlineStr">
+      <c r="C33" s="14" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>

--- a/tools/keybind_sheet/MidnightHelper_Keybinds.xlsx
+++ b/tools/keybind_sheet/MidnightHelper_Keybinds.xlsx
@@ -16933,7 +16933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17516,6 +17516,23 @@
       <c r="C34" s="13" t="inlineStr">
         <is>
           <t>Defensive</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+V</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Disrupting Shout</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
